--- a/processed_data/hard_data_exports/hunt_tables/2026/2026_DEER_BUCK.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/2026_DEER_BUCK.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_deer_buck" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026_deer_buck" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_deer_buck'!$A$3:$J$462</definedName>
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J462"/>
+  <dimension ref="A1:N462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -614,6 +614,26 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Prior Year</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Success (Prior Year %)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Average Harvest Age (Prior Year)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Average Days Hunted (Prior Year)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -894,6 +914,20 @@
       <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" s="6" t="inlineStr"/>
       <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -934,6 +968,20 @@
       <c r="H11" s="8" t="inlineStr"/>
       <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1146,6 +1194,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -1198,6 +1260,20 @@
           <t>29</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>67.6</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1250,6 +1326,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -1302,6 +1392,20 @@
           <t>27</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -1354,6 +1458,20 @@
           <t>83</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -1406,6 +1524,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -1458,6 +1590,20 @@
           <t>29</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -1510,6 +1656,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -1562,6 +1722,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -1614,6 +1788,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -1666,6 +1854,20 @@
           <t>33</t>
         </is>
       </c>
+      <c r="K26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>92.9</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -1718,6 +1920,20 @@
           <t>61</t>
         </is>
       </c>
+      <c r="K27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -1770,6 +1986,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>84.6</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -1822,6 +2052,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -1874,6 +2118,20 @@
           <t>17</t>
         </is>
       </c>
+      <c r="K30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
@@ -1926,6 +2184,20 @@
           <t>24</t>
         </is>
       </c>
+      <c r="K31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -1978,6 +2250,20 @@
           <t>51</t>
         </is>
       </c>
+      <c r="K32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>56.9</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
@@ -2030,6 +2316,20 @@
           <t>152</t>
         </is>
       </c>
+      <c r="K33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -2082,6 +2382,20 @@
           <t>38</t>
         </is>
       </c>
+      <c r="K34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
@@ -2134,6 +2448,20 @@
           <t>37</t>
         </is>
       </c>
+      <c r="K35" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -2186,6 +2514,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -2238,6 +2580,20 @@
           <t>47</t>
         </is>
       </c>
+      <c r="K37" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>88.9</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -2290,6 +2646,20 @@
           <t>68</t>
         </is>
       </c>
+      <c r="K38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>96.9</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
@@ -2342,6 +2712,20 @@
           <t>144</t>
         </is>
       </c>
+      <c r="K39" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -2394,6 +2778,20 @@
           <t>61</t>
         </is>
       </c>
+      <c r="K40" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
@@ -2446,6 +2844,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K41" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -2498,6 +2910,20 @@
           <t>12</t>
         </is>
       </c>
+      <c r="K42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
@@ -2550,6 +2976,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -2602,6 +3042,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
@@ -2654,6 +3108,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K45" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -2706,6 +3174,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K46" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
@@ -2758,6 +3240,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -2810,6 +3306,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
@@ -2862,6 +3372,20 @@
           <t>17</t>
         </is>
       </c>
+      <c r="K49" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -2914,6 +3438,20 @@
           <t>24</t>
         </is>
       </c>
+      <c r="K50" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
@@ -2966,6 +3504,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -3018,6 +3570,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
@@ -3070,6 +3636,20 @@
           <t>33</t>
         </is>
       </c>
+      <c r="K53" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>63.3</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -3122,6 +3702,20 @@
           <t>51</t>
         </is>
       </c>
+      <c r="K54" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
@@ -3174,6 +3768,20 @@
           <t>17</t>
         </is>
       </c>
+      <c r="K55" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>46.7</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="48" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -3226,6 +3834,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="48" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
@@ -3278,6 +3900,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>30.3</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="48" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -3330,6 +3966,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K58" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="48" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
@@ -3382,6 +4032,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="48" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -3434,6 +4098,20 @@
           <t>8</t>
         </is>
       </c>
+      <c r="K60" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
@@ -3486,6 +4164,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K61" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -3538,6 +4230,20 @@
           <t>14</t>
         </is>
       </c>
+      <c r="K62" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
@@ -3588,6 +4294,20 @@
       <c r="J63" s="8" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3630,6 +4350,20 @@
       <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
@@ -3682,6 +4416,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K65" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -3734,6 +4482,20 @@
           <t>16</t>
         </is>
       </c>
+      <c r="K66" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
@@ -3786,6 +4548,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>88.9</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -3836,6 +4612,20 @@
       <c r="J68" s="6" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>6.3</t>
         </is>
       </c>
     </row>
@@ -3878,6 +4668,20 @@
       <c r="H69" s="8" t="inlineStr"/>
       <c r="I69" s="8" t="inlineStr"/>
       <c r="J69" s="8" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -3918,6 +4722,20 @@
       <c r="H70" s="6" t="inlineStr"/>
       <c r="I70" s="6" t="inlineStr"/>
       <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
@@ -3970,6 +4788,20 @@
           <t>26</t>
         </is>
       </c>
+      <c r="K71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -4022,6 +4854,20 @@
           <t>12</t>
         </is>
       </c>
+      <c r="K72" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
@@ -4074,6 +4920,20 @@
           <t>45</t>
         </is>
       </c>
+      <c r="K73" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -4126,6 +4986,20 @@
           <t>26</t>
         </is>
       </c>
+      <c r="K74" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
@@ -4178,6 +5052,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K75" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -4230,6 +5118,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K76" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
@@ -4282,6 +5184,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -4334,6 +5250,20 @@
           <t>14</t>
         </is>
       </c>
+      <c r="K78" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
@@ -4386,6 +5316,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K79" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -4438,6 +5382,20 @@
           <t>40</t>
         </is>
       </c>
+      <c r="K80" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="32" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
@@ -4490,6 +5448,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K81" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="32" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -4542,6 +5514,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K82" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
@@ -4594,6 +5580,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K83" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -4646,6 +5646,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K84" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
@@ -4698,6 +5712,20 @@
           <t>8</t>
         </is>
       </c>
+      <c r="K85" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="32" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -4750,6 +5778,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K86" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
@@ -4802,6 +5844,20 @@
           <t>22</t>
         </is>
       </c>
+      <c r="K87" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -4854,6 +5910,20 @@
           <t>22</t>
         </is>
       </c>
+      <c r="K88" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>27.8</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
@@ -4906,6 +5976,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K89" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="48" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -4958,6 +6042,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K90" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
@@ -5010,6 +6108,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K91" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
@@ -5062,6 +6174,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K92" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
@@ -5114,6 +6240,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K93" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -5166,6 +6306,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K94" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
@@ -5218,6 +6372,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K95" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -5270,6 +6438,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K96" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="32" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
@@ -5320,6 +6502,20 @@
       <c r="J97" s="8" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>13.8</t>
         </is>
       </c>
     </row>
@@ -5414,6 +6610,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K99" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="24" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
@@ -5466,6 +6676,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K100" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
@@ -5570,6 +6794,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K102" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
@@ -5622,6 +6860,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K103" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
@@ -5674,6 +6926,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K104" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
@@ -5726,6 +6992,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K105" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
@@ -5778,6 +7058,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K106" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
@@ -5830,6 +7124,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K107" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
@@ -5882,6 +7190,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
@@ -5934,6 +7256,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K109" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
@@ -5986,6 +7322,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
@@ -6038,6 +7388,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
@@ -6090,6 +7454,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
@@ -6142,6 +7520,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
@@ -6194,6 +7586,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K114" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="24" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
@@ -6246,6 +7652,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
@@ -6298,6 +7718,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
@@ -6350,6 +7784,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
@@ -6402,6 +7850,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
@@ -6454,6 +7916,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="24" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
@@ -6506,6 +7982,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
@@ -6558,6 +8048,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K121" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
@@ -6610,6 +8114,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
@@ -6662,6 +8180,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K123" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
@@ -6714,6 +8246,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K124" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="24" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
@@ -6766,6 +8312,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K125" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
@@ -6818,6 +8378,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>71.4</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
@@ -6870,6 +8444,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="24" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
@@ -6922,6 +8510,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="24" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
@@ -6974,6 +8576,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="24" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
@@ -7026,6 +8642,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
@@ -7078,6 +8708,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>76.9</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="24" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
@@ -7130,6 +8774,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K132" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="24" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
@@ -7182,6 +8840,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K133" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
@@ -7234,6 +8906,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K134" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="24" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
@@ -7286,6 +8972,20 @@
           <t>14</t>
         </is>
       </c>
+      <c r="K135" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="24" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
@@ -7338,6 +9038,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K136" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="24" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
@@ -7390,6 +9104,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>71.4</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="24" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
@@ -7442,6 +9170,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K138" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
@@ -7494,6 +9236,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="24" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
@@ -7546,6 +9302,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="24" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
@@ -7598,6 +9368,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="24" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
@@ -7650,6 +9434,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="24" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
@@ -7702,6 +9500,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="24" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
@@ -7754,6 +9566,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K144" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="24" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
@@ -7806,6 +9632,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="24" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
@@ -7858,6 +9698,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="24" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
@@ -7910,6 +9764,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="24" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
@@ -7962,6 +9830,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="24" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
@@ -8014,6 +9896,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="24" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
@@ -8066,6 +9962,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="24" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
@@ -8118,6 +10028,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K151" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="24" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
@@ -8170,6 +10094,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="24" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
@@ -8222,6 +10160,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="24" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
@@ -8274,6 +10226,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="24" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
@@ -8326,6 +10292,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="24" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
@@ -8378,6 +10358,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="24" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
@@ -8430,6 +10424,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K157" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="24" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
@@ -8482,6 +10490,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K158" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="24" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
@@ -8534,6 +10556,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K159" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="24" customHeight="1">
       <c r="A160" s="5" t="inlineStr">
@@ -8586,6 +10622,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K160" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>73.9</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="24" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
@@ -8638,6 +10688,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K161" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="24" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
@@ -8690,6 +10754,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K162" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="24" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
@@ -8742,6 +10820,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K163" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="24" customHeight="1">
       <c r="A164" s="5" t="inlineStr">
@@ -8794,6 +10886,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K164" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="24" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
@@ -8846,6 +10952,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K165" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="24" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
@@ -8898,6 +11018,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K166" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="24" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
@@ -8950,6 +11084,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K167" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="24" customHeight="1">
       <c r="A168" s="5" t="inlineStr">
@@ -9002,6 +11150,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K168" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="24" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
@@ -9054,6 +11216,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K169" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="24" customHeight="1">
       <c r="A170" s="5" t="inlineStr">
@@ -9106,6 +11282,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K170" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="24" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
@@ -9158,6 +11348,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K171" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="24" customHeight="1">
       <c r="A172" s="5" t="inlineStr">
@@ -9210,6 +11414,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K172" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="24" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
@@ -9262,6 +11480,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K173" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="24" customHeight="1">
       <c r="A174" s="5" t="inlineStr">
@@ -9314,6 +11546,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K174" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="24" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
@@ -9366,6 +11612,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K175" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="24" customHeight="1">
       <c r="A176" s="5" t="inlineStr">
@@ -9418,6 +11678,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K176" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="24" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
@@ -9470,6 +11744,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K177" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="24" customHeight="1">
       <c r="A178" s="5" t="inlineStr">
@@ -9522,6 +11810,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K178" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="24" customHeight="1">
       <c r="A179" s="7" t="inlineStr">
@@ -9574,6 +11876,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K179" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="24" customHeight="1">
       <c r="A180" s="5" t="inlineStr">
@@ -9626,6 +11942,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K180" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="24" customHeight="1">
       <c r="A181" s="7" t="inlineStr">
@@ -9678,6 +12008,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K181" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>95.7</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="24" customHeight="1">
       <c r="A182" s="5" t="inlineStr">
@@ -9730,6 +12074,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K182" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="24" customHeight="1">
       <c r="A183" s="7" t="inlineStr">
@@ -9782,6 +12140,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K183" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="24" customHeight="1">
       <c r="A184" s="5" t="inlineStr">
@@ -9834,6 +12206,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K184" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="24" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
@@ -9886,6 +12272,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K185" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="24" customHeight="1">
       <c r="A186" s="5" t="inlineStr">
@@ -9938,6 +12338,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K186" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="24" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
@@ -9990,6 +12404,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K187" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="24" customHeight="1">
       <c r="A188" s="5" t="inlineStr">
@@ -10042,6 +12470,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K188" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>92.9</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="24" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
@@ -10094,6 +12536,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K189" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>95.7</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="24" customHeight="1">
       <c r="A190" s="5" t="inlineStr">
@@ -10146,6 +12602,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K190" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="24" customHeight="1">
       <c r="A191" s="7" t="inlineStr">
@@ -10198,6 +12668,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K191" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="24" customHeight="1">
       <c r="A192" s="5" t="inlineStr">
@@ -10250,6 +12734,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K192" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="24" customHeight="1">
       <c r="A193" s="7" t="inlineStr">
@@ -10302,6 +12800,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K193" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="24" customHeight="1">
       <c r="A194" s="5" t="inlineStr">
@@ -10354,6 +12866,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K194" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="24" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
@@ -10406,6 +12932,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K195" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="24" customHeight="1">
       <c r="A196" s="5" t="inlineStr">
@@ -10458,6 +12998,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K196" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="24" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
@@ -10510,6 +13064,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K197" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>71.4</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="24" customHeight="1">
       <c r="A198" s="5" t="inlineStr">
@@ -10562,6 +13130,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K198" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="24" customHeight="1">
       <c r="A199" s="7" t="inlineStr">
@@ -10614,6 +13196,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K199" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="24" customHeight="1">
       <c r="A200" s="5" t="inlineStr">
@@ -10666,6 +13262,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K200" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="24" customHeight="1">
       <c r="A201" s="7" t="inlineStr">
@@ -10718,6 +13328,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K201" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="24" customHeight="1">
       <c r="A202" s="5" t="inlineStr">
@@ -10770,6 +13394,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K202" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>31.3</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="24" customHeight="1">
       <c r="A203" s="7" t="inlineStr">
@@ -10822,6 +13460,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K203" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="24" customHeight="1">
       <c r="A204" s="5" t="inlineStr">
@@ -10874,6 +13526,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K204" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="24" customHeight="1">
       <c r="A205" s="7" t="inlineStr">
@@ -10926,6 +13592,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K205" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="24" customHeight="1">
       <c r="A206" s="5" t="inlineStr">
@@ -10978,6 +13658,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K206" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="24" customHeight="1">
       <c r="A207" s="7" t="inlineStr">
@@ -11030,6 +13724,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K207" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="24" customHeight="1">
       <c r="A208" s="5" t="inlineStr">
@@ -11082,6 +13790,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K208" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="24" customHeight="1">
       <c r="A209" s="7" t="inlineStr">
@@ -11134,6 +13856,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K209" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="32" customHeight="1">
       <c r="A210" s="5" t="inlineStr">
@@ -11184,6 +13920,20 @@
       <c r="J210" s="6" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="K210" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>3.5</t>
         </is>
       </c>
     </row>
@@ -11282,6 +14032,20 @@
           <t>1040</t>
         </is>
       </c>
+      <c r="K212" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="24" customHeight="1">
       <c r="A213" s="7" t="inlineStr">
@@ -11326,6 +14090,20 @@
           <t>1160</t>
         </is>
       </c>
+      <c r="K213" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="24" customHeight="1">
       <c r="A214" s="5" t="inlineStr">
@@ -11370,6 +14148,20 @@
           <t>1800</t>
         </is>
       </c>
+      <c r="K214" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="24" customHeight="1">
       <c r="A215" s="7" t="inlineStr">
@@ -11414,6 +14206,20 @@
           <t>1060</t>
         </is>
       </c>
+      <c r="K215" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="24" customHeight="1">
       <c r="A216" s="5" t="inlineStr">
@@ -11458,6 +14264,20 @@
           <t>460</t>
         </is>
       </c>
+      <c r="K216" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="24" customHeight="1">
       <c r="A217" s="7" t="inlineStr">
@@ -11502,6 +14322,20 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K217" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="24" customHeight="1">
       <c r="A218" s="5" t="inlineStr">
@@ -11546,6 +14380,20 @@
           <t>360</t>
         </is>
       </c>
+      <c r="K218" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>48.3</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="24" customHeight="1">
       <c r="A219" s="7" t="inlineStr">
@@ -11590,6 +14438,20 @@
           <t>220</t>
         </is>
       </c>
+      <c r="K219" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="24" customHeight="1">
       <c r="A220" s="5" t="inlineStr">
@@ -11634,6 +14496,20 @@
           <t>80</t>
         </is>
       </c>
+      <c r="K220" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="24" customHeight="1">
       <c r="A221" s="7" t="inlineStr">
@@ -11678,6 +14554,20 @@
           <t>280</t>
         </is>
       </c>
+      <c r="K221" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="24" customHeight="1">
       <c r="A222" s="5" t="inlineStr">
@@ -11722,6 +14612,20 @@
           <t>620</t>
         </is>
       </c>
+      <c r="K222" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="24" customHeight="1">
       <c r="A223" s="7" t="inlineStr">
@@ -11766,6 +14670,20 @@
           <t>540</t>
         </is>
       </c>
+      <c r="K223" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="24" customHeight="1">
       <c r="A224" s="5" t="inlineStr">
@@ -11810,6 +14728,20 @@
           <t>500</t>
         </is>
       </c>
+      <c r="K224" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>36.7</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="24" customHeight="1">
       <c r="A225" s="7" t="inlineStr">
@@ -11854,6 +14786,20 @@
           <t>600</t>
         </is>
       </c>
+      <c r="K225" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="24" customHeight="1">
       <c r="A226" s="5" t="inlineStr">
@@ -11898,6 +14844,20 @@
           <t>720</t>
         </is>
       </c>
+      <c r="K226" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="24" customHeight="1">
       <c r="A227" s="7" t="inlineStr">
@@ -11942,6 +14902,20 @@
           <t>260</t>
         </is>
       </c>
+      <c r="K227" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="24" customHeight="1">
       <c r="A228" s="5" t="inlineStr">
@@ -11986,6 +14960,20 @@
           <t>560</t>
         </is>
       </c>
+      <c r="K228" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>37.6</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="24" customHeight="1">
       <c r="A229" s="7" t="inlineStr">
@@ -12030,6 +15018,20 @@
           <t>420</t>
         </is>
       </c>
+      <c r="K229" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="24" customHeight="1">
       <c r="A230" s="5" t="inlineStr">
@@ -12074,6 +15076,20 @@
           <t>280</t>
         </is>
       </c>
+      <c r="K230" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>30.2</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="24" customHeight="1">
       <c r="A231" s="7" t="inlineStr">
@@ -12118,6 +15134,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K231" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="24" customHeight="1">
       <c r="A232" s="5" t="inlineStr">
@@ -12162,6 +15192,20 @@
           <t>1300</t>
         </is>
       </c>
+      <c r="K232" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="24" customHeight="1">
       <c r="A233" s="7" t="inlineStr">
@@ -12206,6 +15250,20 @@
           <t>1580</t>
         </is>
       </c>
+      <c r="K233" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="24" customHeight="1">
       <c r="A234" s="5" t="inlineStr">
@@ -12250,6 +15308,20 @@
           <t>675</t>
         </is>
       </c>
+      <c r="K234" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="24" customHeight="1">
       <c r="A235" s="7" t="inlineStr">
@@ -12294,6 +15366,20 @@
           <t>2080</t>
         </is>
       </c>
+      <c r="K235" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="24" customHeight="1">
       <c r="A236" s="5" t="inlineStr">
@@ -12338,6 +15424,20 @@
           <t>5400</t>
         </is>
       </c>
+      <c r="K236" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>47.3</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="24" customHeight="1">
       <c r="A237" s="7" t="inlineStr">
@@ -12382,6 +15482,20 @@
           <t>3180</t>
         </is>
       </c>
+      <c r="K237" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="24" customHeight="1">
       <c r="A238" s="5" t="inlineStr">
@@ -12426,6 +15540,20 @@
           <t>920</t>
         </is>
       </c>
+      <c r="K238" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="24" customHeight="1">
       <c r="A239" s="7" t="inlineStr">
@@ -12470,6 +15598,20 @@
           <t>400</t>
         </is>
       </c>
+      <c r="K239" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="24" customHeight="1">
       <c r="A240" s="5" t="inlineStr">
@@ -12514,6 +15656,20 @@
           <t>1080</t>
         </is>
       </c>
+      <c r="K240" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="24" customHeight="1">
       <c r="A241" s="7" t="inlineStr">
@@ -12558,6 +15714,20 @@
           <t>660</t>
         </is>
       </c>
+      <c r="K241" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="24" customHeight="1">
       <c r="A242" s="5" t="inlineStr">
@@ -12602,6 +15772,20 @@
           <t>240</t>
         </is>
       </c>
+      <c r="K242" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="24" customHeight="1">
       <c r="A243" s="7" t="inlineStr">
@@ -12646,6 +15830,20 @@
           <t>560</t>
         </is>
       </c>
+      <c r="K243" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="24" customHeight="1">
       <c r="A244" s="5" t="inlineStr">
@@ -12690,6 +15888,20 @@
           <t>1240</t>
         </is>
       </c>
+      <c r="K244" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>40.9</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="24" customHeight="1">
       <c r="A245" s="7" t="inlineStr">
@@ -12734,6 +15946,20 @@
           <t>1620</t>
         </is>
       </c>
+      <c r="K245" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="24" customHeight="1">
       <c r="A246" s="5" t="inlineStr">
@@ -12778,6 +16004,20 @@
           <t>1000</t>
         </is>
       </c>
+      <c r="K246" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="24" customHeight="1">
       <c r="A247" s="7" t="inlineStr">
@@ -12822,6 +16062,20 @@
           <t>1200</t>
         </is>
       </c>
+      <c r="K247" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="24" customHeight="1">
       <c r="A248" s="5" t="inlineStr">
@@ -12866,6 +16120,20 @@
           <t>520</t>
         </is>
       </c>
+      <c r="K248" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="24" customHeight="1">
       <c r="A249" s="7" t="inlineStr">
@@ -12910,6 +16178,20 @@
           <t>1680</t>
         </is>
       </c>
+      <c r="K249" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="24" customHeight="1">
       <c r="A250" s="5" t="inlineStr">
@@ -12954,6 +16236,20 @@
           <t>700</t>
         </is>
       </c>
+      <c r="K250" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="24" customHeight="1">
       <c r="A251" s="7" t="inlineStr">
@@ -12998,6 +16294,20 @@
           <t>840</t>
         </is>
       </c>
+      <c r="K251" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>63.1</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="24" customHeight="1">
       <c r="A252" s="5" t="inlineStr">
@@ -13042,6 +16352,20 @@
           <t>300</t>
         </is>
       </c>
+      <c r="K252" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>43.3</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="24" customHeight="1">
       <c r="A253" s="7" t="inlineStr">
@@ -13086,6 +16410,20 @@
           <t>3900</t>
         </is>
       </c>
+      <c r="K253" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>42.8</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="24" customHeight="1">
       <c r="A254" s="5" t="inlineStr">
@@ -13130,6 +16468,20 @@
           <t>4740</t>
         </is>
       </c>
+      <c r="K254" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>28.2</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="24" customHeight="1">
       <c r="A255" s="7" t="inlineStr">
@@ -13174,6 +16526,20 @@
           <t>1350</t>
         </is>
       </c>
+      <c r="K255" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>62.2</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="24" customHeight="1">
       <c r="A256" s="5" t="inlineStr">
@@ -13218,6 +16584,20 @@
           <t>1040</t>
         </is>
       </c>
+      <c r="K256" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="24" customHeight="1">
       <c r="A257" s="7" t="inlineStr">
@@ -13262,6 +16642,20 @@
           <t>1800</t>
         </is>
       </c>
+      <c r="K257" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="24" customHeight="1">
       <c r="A258" s="5" t="inlineStr">
@@ -13306,6 +16700,20 @@
           <t>1060</t>
         </is>
       </c>
+      <c r="K258" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="24" customHeight="1">
       <c r="A259" s="7" t="inlineStr">
@@ -13350,6 +16758,20 @@
           <t>460</t>
         </is>
       </c>
+      <c r="K259" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="24" customHeight="1">
       <c r="A260" s="5" t="inlineStr">
@@ -13394,6 +16816,20 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K260" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="24" customHeight="1">
       <c r="A261" s="7" t="inlineStr">
@@ -13438,6 +16874,20 @@
           <t>360</t>
         </is>
       </c>
+      <c r="K261" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="24" customHeight="1">
       <c r="A262" s="5" t="inlineStr">
@@ -13482,6 +16932,20 @@
           <t>220</t>
         </is>
       </c>
+      <c r="K262" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="24" customHeight="1">
       <c r="A263" s="7" t="inlineStr">
@@ -13526,6 +16990,20 @@
           <t>80</t>
         </is>
       </c>
+      <c r="K263" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="24" customHeight="1">
       <c r="A264" s="5" t="inlineStr">
@@ -13570,6 +17048,20 @@
           <t>280</t>
         </is>
       </c>
+      <c r="K264" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="24" customHeight="1">
       <c r="A265" s="7" t="inlineStr">
@@ -13614,6 +17106,20 @@
           <t>620</t>
         </is>
       </c>
+      <c r="K265" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="24" customHeight="1">
       <c r="A266" s="5" t="inlineStr">
@@ -13658,6 +17164,20 @@
           <t>540</t>
         </is>
       </c>
+      <c r="K266" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="24" customHeight="1">
       <c r="A267" s="7" t="inlineStr">
@@ -13702,6 +17222,20 @@
           <t>500</t>
         </is>
       </c>
+      <c r="K267" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>40.8</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="24" customHeight="1">
       <c r="A268" s="5" t="inlineStr">
@@ -13746,6 +17280,20 @@
           <t>600</t>
         </is>
       </c>
+      <c r="K268" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>32.6</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="24" customHeight="1">
       <c r="A269" s="7" t="inlineStr">
@@ -13790,6 +17338,20 @@
           <t>260</t>
         </is>
       </c>
+      <c r="K269" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="24" customHeight="1">
       <c r="A270" s="5" t="inlineStr">
@@ -13834,6 +17396,20 @@
           <t>560</t>
         </is>
       </c>
+      <c r="K270" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>44.5</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="24" customHeight="1">
       <c r="A271" s="7" t="inlineStr">
@@ -13878,6 +17454,20 @@
           <t>280</t>
         </is>
       </c>
+      <c r="K271" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="24" customHeight="1">
       <c r="A272" s="5" t="inlineStr">
@@ -13922,6 +17512,20 @@
           <t>280</t>
         </is>
       </c>
+      <c r="K272" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>43.6</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="24" customHeight="1">
       <c r="A273" s="7" t="inlineStr">
@@ -13966,6 +17570,20 @@
           <t>100</t>
         </is>
       </c>
+      <c r="K273" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="24" customHeight="1">
       <c r="A274" s="5" t="inlineStr">
@@ -14010,6 +17628,20 @@
           <t>1300</t>
         </is>
       </c>
+      <c r="K274" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>27.5</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="24" customHeight="1">
       <c r="A275" s="7" t="inlineStr">
@@ -14054,6 +17686,20 @@
           <t>1580</t>
         </is>
       </c>
+      <c r="K275" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="24" customHeight="1">
       <c r="A276" s="5" t="inlineStr">
@@ -14098,6 +17744,20 @@
           <t>675</t>
         </is>
       </c>
+      <c r="K276" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>43.7</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="24" customHeight="1">
       <c r="A277" s="7" t="inlineStr">
@@ -14142,6 +17802,20 @@
           <t>460</t>
         </is>
       </c>
+      <c r="K277" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>48.6</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="24" customHeight="1">
       <c r="A278" s="5" t="inlineStr">
@@ -14186,6 +17860,20 @@
           <t>200</t>
         </is>
       </c>
+      <c r="K278" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="24" customHeight="1">
       <c r="A279" s="7" t="inlineStr">
@@ -14230,6 +17918,20 @@
           <t>280</t>
         </is>
       </c>
+      <c r="K279" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>36.5</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="24" customHeight="1">
       <c r="A280" s="5" t="inlineStr">
@@ -14274,6 +17976,20 @@
           <t>500</t>
         </is>
       </c>
+      <c r="K280" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="24" customHeight="1">
       <c r="A281" s="7" t="inlineStr">
@@ -14318,6 +18034,20 @@
           <t>600</t>
         </is>
       </c>
+      <c r="K281" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>35.4</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="24" customHeight="1">
       <c r="A282" s="5" t="inlineStr">
@@ -14362,6 +18092,20 @@
           <t>260</t>
         </is>
       </c>
+      <c r="K282" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="24" customHeight="1">
       <c r="A283" s="7" t="inlineStr">
@@ -14406,6 +18150,20 @@
           <t>675</t>
         </is>
       </c>
+      <c r="K283" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="24" customHeight="1">
       <c r="A284" s="5" t="inlineStr">
@@ -14450,6 +18208,20 @@
           <t>620</t>
         </is>
       </c>
+      <c r="K284" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="24" customHeight="1">
       <c r="A285" s="7" t="inlineStr">
@@ -14494,6 +18266,20 @@
           <t>880</t>
         </is>
       </c>
+      <c r="K285" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="24" customHeight="1">
       <c r="A286" s="5" t="inlineStr">
@@ -14538,6 +18324,20 @@
           <t>440</t>
         </is>
       </c>
+      <c r="K286" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="24" customHeight="1">
       <c r="A287" s="7" t="inlineStr">
@@ -14582,6 +18382,20 @@
           <t>440</t>
         </is>
       </c>
+      <c r="K287" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="24" customHeight="1">
       <c r="A288" s="5" t="inlineStr">
@@ -14626,6 +18440,20 @@
           <t>440</t>
         </is>
       </c>
+      <c r="K288" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="24" customHeight="1">
       <c r="A289" s="7" t="inlineStr">
@@ -14670,6 +18498,20 @@
           <t>760</t>
         </is>
       </c>
+      <c r="K289" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="24" customHeight="1">
       <c r="A290" s="5" t="inlineStr">
@@ -14714,6 +18556,20 @@
           <t>380</t>
         </is>
       </c>
+      <c r="K290" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="24" customHeight="1">
       <c r="A291" s="7" t="inlineStr">
@@ -14758,6 +18614,20 @@
           <t>380</t>
         </is>
       </c>
+      <c r="K291" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="24" customHeight="1">
       <c r="A292" s="5" t="inlineStr">
@@ -14802,6 +18672,20 @@
           <t>380</t>
         </is>
       </c>
+      <c r="K292" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="24" customHeight="1">
       <c r="A293" s="7" t="inlineStr">
@@ -14846,6 +18730,20 @@
           <t>640</t>
         </is>
       </c>
+      <c r="K293" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="24" customHeight="1">
       <c r="A294" s="5" t="inlineStr">
@@ -14890,6 +18788,20 @@
           <t>320</t>
         </is>
       </c>
+      <c r="K294" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>13.9</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="24" customHeight="1">
       <c r="A295" s="7" t="inlineStr">
@@ -14934,6 +18846,20 @@
           <t>320</t>
         </is>
       </c>
+      <c r="K295" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="24" customHeight="1">
       <c r="A296" s="5" t="inlineStr">
@@ -14978,6 +18904,20 @@
           <t>320</t>
         </is>
       </c>
+      <c r="K296" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="24" customHeight="1">
       <c r="A297" s="7" t="inlineStr">
@@ -15022,6 +18962,20 @@
           <t>440</t>
         </is>
       </c>
+      <c r="K297" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="24" customHeight="1">
       <c r="A298" s="5" t="inlineStr">
@@ -15066,6 +19020,20 @@
           <t>440</t>
         </is>
       </c>
+      <c r="K298" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="24" customHeight="1">
       <c r="A299" s="7" t="inlineStr">
@@ -15110,6 +19078,20 @@
           <t>1320</t>
         </is>
       </c>
+      <c r="K299" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="24" customHeight="1">
       <c r="A300" s="5" t="inlineStr">
@@ -15154,6 +19136,20 @@
           <t>130</t>
         </is>
       </c>
+      <c r="K300" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>28.2</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="24" customHeight="1">
       <c r="A301" s="7" t="inlineStr">
@@ -15198,6 +19194,20 @@
           <t>130</t>
         </is>
       </c>
+      <c r="K301" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>39.2</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="24" customHeight="1">
       <c r="A302" s="5" t="inlineStr">
@@ -15242,6 +19252,20 @@
           <t>390</t>
         </is>
       </c>
+      <c r="K302" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="24" customHeight="1">
       <c r="A303" s="7" t="inlineStr">
@@ -15286,6 +19310,20 @@
           <t>80</t>
         </is>
       </c>
+      <c r="K303" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="24" customHeight="1">
       <c r="A304" s="5" t="inlineStr">
@@ -15330,6 +19368,20 @@
           <t>80</t>
         </is>
       </c>
+      <c r="K304" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="24" customHeight="1">
       <c r="A305" s="7" t="inlineStr">
@@ -15374,6 +19426,20 @@
           <t>240</t>
         </is>
       </c>
+      <c r="K305" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="24" customHeight="1">
       <c r="A306" s="5" t="inlineStr">
@@ -15418,6 +19484,20 @@
           <t>450</t>
         </is>
       </c>
+      <c r="K306" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>27.1</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="24" customHeight="1">
       <c r="A307" s="7" t="inlineStr">
@@ -15462,6 +19542,20 @@
           <t>450</t>
         </is>
       </c>
+      <c r="K307" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="24" customHeight="1">
       <c r="A308" s="5" t="inlineStr">
@@ -15506,6 +19600,20 @@
           <t>1350</t>
         </is>
       </c>
+      <c r="K308" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>47.1</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="24" customHeight="1">
       <c r="A309" s="7" t="inlineStr">
@@ -15550,6 +19658,20 @@
           <t>250</t>
         </is>
       </c>
+      <c r="K309" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>25.8</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="24" customHeight="1">
       <c r="A310" s="5" t="inlineStr">
@@ -15594,6 +19716,20 @@
           <t>250</t>
         </is>
       </c>
+      <c r="K310" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="24" customHeight="1">
       <c r="A311" s="7" t="inlineStr">
@@ -15638,6 +19774,20 @@
           <t>750</t>
         </is>
       </c>
+      <c r="K311" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="24" customHeight="1">
       <c r="A312" s="5" t="inlineStr">
@@ -15682,6 +19832,20 @@
           <t>3480</t>
         </is>
       </c>
+      <c r="K312" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="24" customHeight="1">
       <c r="A313" s="7" t="inlineStr">
@@ -15726,6 +19890,20 @@
           <t>1160</t>
         </is>
       </c>
+      <c r="K313" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>25.9</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="24" customHeight="1">
       <c r="A314" s="5" t="inlineStr">
@@ -15770,6 +19948,20 @@
           <t>960</t>
         </is>
       </c>
+      <c r="K314" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>40.9</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="24" customHeight="1">
       <c r="A315" s="7" t="inlineStr">
@@ -15814,6 +20006,20 @@
           <t>720</t>
         </is>
       </c>
+      <c r="K315" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>32.4</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="24" customHeight="1">
       <c r="A316" s="5" t="inlineStr">
@@ -15858,6 +20064,20 @@
           <t>1040</t>
         </is>
       </c>
+      <c r="K316" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="54" customHeight="1">
       <c r="A317" s="7" t="inlineStr">
@@ -15902,6 +20122,20 @@
           <t>688</t>
         </is>
       </c>
+      <c r="K317" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>37.2</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="54" customHeight="1">
       <c r="A318" s="5" t="inlineStr">
@@ -15946,6 +20180,20 @@
           <t>588</t>
         </is>
       </c>
+      <c r="K318" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="48" customHeight="1">
       <c r="A319" s="7" t="inlineStr">
@@ -15990,6 +20238,20 @@
           <t>573</t>
         </is>
       </c>
+      <c r="K319" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>39.2</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="48" customHeight="1">
       <c r="A320" s="5" t="inlineStr">
@@ -16034,6 +20296,20 @@
           <t>349</t>
         </is>
       </c>
+      <c r="K320" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>39.6</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="54" customHeight="1">
       <c r="A321" s="7" t="inlineStr">
@@ -16078,6 +20354,20 @@
           <t>42</t>
         </is>
       </c>
+      <c r="K321" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>43.3</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="54" customHeight="1">
       <c r="A322" s="5" t="inlineStr">
@@ -16122,6 +20412,20 @@
           <t>55</t>
         </is>
       </c>
+      <c r="K322" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="48" customHeight="1">
       <c r="A323" s="7" t="inlineStr">
@@ -16166,6 +20470,20 @@
           <t>67</t>
         </is>
       </c>
+      <c r="K323" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>47.7</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="48" customHeight="1">
       <c r="A324" s="5" t="inlineStr">
@@ -16210,6 +20528,20 @@
           <t>45</t>
         </is>
       </c>
+      <c r="K324" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="48" customHeight="1">
       <c r="A325" s="7" t="inlineStr">
@@ -16254,6 +20586,20 @@
           <t>26</t>
         </is>
       </c>
+      <c r="K325" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="54" customHeight="1">
       <c r="A326" s="5" t="inlineStr">
@@ -16298,6 +20644,20 @@
           <t>62</t>
         </is>
       </c>
+      <c r="K326" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>40.4</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="54" customHeight="1">
       <c r="A327" s="7" t="inlineStr">
@@ -16342,6 +20702,20 @@
           <t>340</t>
         </is>
       </c>
+      <c r="K327" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="48" customHeight="1">
       <c r="A328" s="5" t="inlineStr">
@@ -16386,6 +20760,20 @@
           <t>297</t>
         </is>
       </c>
+      <c r="K328" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="54" customHeight="1">
       <c r="A329" s="7" t="inlineStr">
@@ -16430,6 +20818,20 @@
           <t>112</t>
         </is>
       </c>
+      <c r="K329" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>40.4</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="54" customHeight="1">
       <c r="A330" s="5" t="inlineStr">
@@ -16474,6 +20876,20 @@
           <t>228</t>
         </is>
       </c>
+      <c r="K330" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="54" customHeight="1">
       <c r="A331" s="7" t="inlineStr">
@@ -16518,6 +20934,20 @@
           <t>70</t>
         </is>
       </c>
+      <c r="K331" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="54" customHeight="1">
       <c r="A332" s="5" t="inlineStr">
@@ -16562,6 +20992,20 @@
           <t>49</t>
         </is>
       </c>
+      <c r="K332" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>39.6</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="48" customHeight="1">
       <c r="A333" s="7" t="inlineStr">
@@ -16606,6 +21050,20 @@
           <t>261</t>
         </is>
       </c>
+      <c r="K333" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>32.1</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="48" customHeight="1">
       <c r="A334" s="5" t="inlineStr">
@@ -16650,6 +21108,20 @@
           <t>45</t>
         </is>
       </c>
+      <c r="K334" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>47.9</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="48" customHeight="1">
       <c r="A335" s="7" t="inlineStr">
@@ -16694,6 +21166,20 @@
           <t>63</t>
         </is>
       </c>
+      <c r="K335" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>37.1</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="48" customHeight="1">
       <c r="A336" s="5" t="inlineStr">
@@ -16738,6 +21224,20 @@
           <t>46</t>
         </is>
       </c>
+      <c r="K336" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="48" customHeight="1">
       <c r="A337" s="7" t="inlineStr">
@@ -16782,6 +21282,20 @@
           <t>271</t>
         </is>
       </c>
+      <c r="K337" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>32.6</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="48" customHeight="1">
       <c r="A338" s="5" t="inlineStr">
@@ -16826,6 +21340,20 @@
           <t>701</t>
         </is>
       </c>
+      <c r="K338" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="54" customHeight="1">
       <c r="A339" s="7" t="inlineStr">
@@ -16870,6 +21398,20 @@
           <t>256</t>
         </is>
       </c>
+      <c r="K339" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>46.9</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="54" customHeight="1">
       <c r="A340" s="5" t="inlineStr">
@@ -16914,6 +21456,20 @@
           <t>292</t>
         </is>
       </c>
+      <c r="K340" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="54" customHeight="1">
       <c r="A341" s="7" t="inlineStr">
@@ -16958,6 +21514,20 @@
           <t>186</t>
         </is>
       </c>
+      <c r="K341" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="54" customHeight="1">
       <c r="A342" s="5" t="inlineStr">
@@ -17002,6 +21572,20 @@
           <t>211</t>
         </is>
       </c>
+      <c r="K342" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="48" customHeight="1">
       <c r="A343" s="7" t="inlineStr">
@@ -17046,6 +21630,20 @@
           <t>61</t>
         </is>
       </c>
+      <c r="K343" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="54" customHeight="1">
       <c r="A344" s="5" t="inlineStr">
@@ -17090,6 +21688,20 @@
           <t>44</t>
         </is>
       </c>
+      <c r="K344" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>27.8</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="48" customHeight="1">
       <c r="A345" s="7" t="inlineStr">
@@ -17134,6 +21746,20 @@
           <t>42</t>
         </is>
       </c>
+      <c r="K345" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="48" customHeight="1">
       <c r="A346" s="5" t="inlineStr">
@@ -17178,6 +21804,20 @@
           <t>65</t>
         </is>
       </c>
+      <c r="K346" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>37.2</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="48" customHeight="1">
       <c r="A347" s="7" t="inlineStr">
@@ -17222,6 +21862,20 @@
           <t>36</t>
         </is>
       </c>
+      <c r="K347" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="32" customHeight="1">
       <c r="A348" s="5" t="inlineStr">
@@ -17262,6 +21916,20 @@
       <c r="H348" s="6" t="inlineStr"/>
       <c r="I348" s="6" t="inlineStr"/>
       <c r="J348" s="6" t="inlineStr"/>
+      <c r="K348" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="32" customHeight="1">
       <c r="A349" s="7" t="inlineStr">
@@ -17302,6 +21970,20 @@
       <c r="H349" s="8" t="inlineStr"/>
       <c r="I349" s="8" t="inlineStr"/>
       <c r="J349" s="8" t="inlineStr"/>
+      <c r="K349" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="32" customHeight="1">
       <c r="A350" s="5" t="inlineStr">
@@ -17342,6 +22024,20 @@
       <c r="H350" s="6" t="inlineStr"/>
       <c r="I350" s="6" t="inlineStr"/>
       <c r="J350" s="6" t="inlineStr"/>
+      <c r="K350" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="32" customHeight="1">
       <c r="A351" s="7" t="inlineStr">
@@ -17382,6 +22078,20 @@
       <c r="H351" s="8" t="inlineStr"/>
       <c r="I351" s="8" t="inlineStr"/>
       <c r="J351" s="8" t="inlineStr"/>
+      <c r="K351" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="32" customHeight="1">
       <c r="A352" s="5" t="inlineStr">
@@ -17422,6 +22132,20 @@
       <c r="H352" s="6" t="inlineStr"/>
       <c r="I352" s="6" t="inlineStr"/>
       <c r="J352" s="6" t="inlineStr"/>
+      <c r="K352" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="32" customHeight="1">
       <c r="A353" s="7" t="inlineStr">
@@ -17462,6 +22186,20 @@
       <c r="H353" s="8" t="inlineStr"/>
       <c r="I353" s="8" t="inlineStr"/>
       <c r="J353" s="8" t="inlineStr"/>
+      <c r="K353" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="48" customHeight="1">
       <c r="A354" s="5" t="inlineStr">
@@ -17542,6 +22280,20 @@
       <c r="H355" s="8" t="inlineStr"/>
       <c r="I355" s="8" t="inlineStr"/>
       <c r="J355" s="8" t="inlineStr"/>
+      <c r="K355" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="48" customHeight="1">
       <c r="A356" s="5" t="inlineStr">
@@ -17582,6 +22334,20 @@
       <c r="H356" s="6" t="inlineStr"/>
       <c r="I356" s="6" t="inlineStr"/>
       <c r="J356" s="6" t="inlineStr"/>
+      <c r="K356" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="357" ht="32" customHeight="1">
       <c r="A357" s="7" t="inlineStr">
@@ -17662,6 +22428,20 @@
       <c r="H358" s="6" t="inlineStr"/>
       <c r="I358" s="6" t="inlineStr"/>
       <c r="J358" s="6" t="inlineStr"/>
+      <c r="K358" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="32" customHeight="1">
       <c r="A359" s="7" t="inlineStr">
@@ -17782,6 +22562,20 @@
       <c r="H361" s="8" t="inlineStr"/>
       <c r="I361" s="8" t="inlineStr"/>
       <c r="J361" s="8" t="inlineStr"/>
+      <c r="K361" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="362" ht="32" customHeight="1">
       <c r="A362" s="5" t="inlineStr">
@@ -17942,6 +22736,20 @@
       <c r="H365" s="8" t="inlineStr"/>
       <c r="I365" s="8" t="inlineStr"/>
       <c r="J365" s="8" t="inlineStr"/>
+      <c r="K365" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="366" ht="32" customHeight="1">
       <c r="A366" s="5" t="inlineStr">
@@ -17982,6 +22790,20 @@
       <c r="H366" s="6" t="inlineStr"/>
       <c r="I366" s="6" t="inlineStr"/>
       <c r="J366" s="6" t="inlineStr"/>
+      <c r="K366" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="32" customHeight="1">
       <c r="A367" s="7" t="inlineStr">
@@ -18062,6 +22884,20 @@
       <c r="H368" s="6" t="inlineStr"/>
       <c r="I368" s="6" t="inlineStr"/>
       <c r="J368" s="6" t="inlineStr"/>
+      <c r="K368" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="32" customHeight="1">
       <c r="A369" s="7" t="inlineStr">
@@ -18102,6 +22938,20 @@
       <c r="H369" s="8" t="inlineStr"/>
       <c r="I369" s="8" t="inlineStr"/>
       <c r="J369" s="8" t="inlineStr"/>
+      <c r="K369" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="370" ht="32" customHeight="1">
       <c r="A370" s="5" t="inlineStr">
@@ -18142,6 +22992,20 @@
       <c r="H370" s="6" t="inlineStr"/>
       <c r="I370" s="6" t="inlineStr"/>
       <c r="J370" s="6" t="inlineStr"/>
+      <c r="K370" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="32" customHeight="1">
       <c r="A371" s="7" t="inlineStr">
@@ -18382,6 +23246,20 @@
       <c r="H376" s="6" t="inlineStr"/>
       <c r="I376" s="6" t="inlineStr"/>
       <c r="J376" s="6" t="inlineStr"/>
+      <c r="K376" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="32" customHeight="1">
       <c r="A377" s="7" t="inlineStr">
@@ -18502,6 +23380,20 @@
       <c r="H379" s="8" t="inlineStr"/>
       <c r="I379" s="8" t="inlineStr"/>
       <c r="J379" s="8" t="inlineStr"/>
+      <c r="K379" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
     </row>
     <row r="380" ht="32" customHeight="1">
       <c r="A380" s="5" t="inlineStr">
@@ -18542,6 +23434,20 @@
       <c r="H380" s="6" t="inlineStr"/>
       <c r="I380" s="6" t="inlineStr"/>
       <c r="J380" s="6" t="inlineStr"/>
+      <c r="K380" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="381" ht="32" customHeight="1">
       <c r="A381" s="7" t="inlineStr">
@@ -18582,6 +23488,20 @@
       <c r="H381" s="8" t="inlineStr"/>
       <c r="I381" s="8" t="inlineStr"/>
       <c r="J381" s="8" t="inlineStr"/>
+      <c r="K381" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="32" customHeight="1">
       <c r="A382" s="5" t="inlineStr">
@@ -18622,6 +23542,20 @@
       <c r="H382" s="6" t="inlineStr"/>
       <c r="I382" s="6" t="inlineStr"/>
       <c r="J382" s="6" t="inlineStr"/>
+      <c r="K382" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="32" customHeight="1">
       <c r="A383" s="7" t="inlineStr">
@@ -18662,6 +23596,20 @@
       <c r="H383" s="8" t="inlineStr"/>
       <c r="I383" s="8" t="inlineStr"/>
       <c r="J383" s="8" t="inlineStr"/>
+      <c r="K383" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>59.4</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="32" customHeight="1">
       <c r="A384" s="5" t="inlineStr">
@@ -18782,6 +23730,20 @@
       <c r="H386" s="6" t="inlineStr"/>
       <c r="I386" s="6" t="inlineStr"/>
       <c r="J386" s="6" t="inlineStr"/>
+      <c r="K386" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="32" customHeight="1">
       <c r="A387" s="7" t="inlineStr">
@@ -18822,6 +23784,20 @@
       <c r="H387" s="8" t="inlineStr"/>
       <c r="I387" s="8" t="inlineStr"/>
       <c r="J387" s="8" t="inlineStr"/>
+      <c r="K387" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="32" customHeight="1">
       <c r="A388" s="5" t="inlineStr">
@@ -18862,6 +23838,20 @@
       <c r="H388" s="6" t="inlineStr"/>
       <c r="I388" s="6" t="inlineStr"/>
       <c r="J388" s="6" t="inlineStr"/>
+      <c r="K388" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
     </row>
     <row r="389" ht="32" customHeight="1">
       <c r="A389" s="7" t="inlineStr">
@@ -18942,6 +23932,20 @@
       <c r="H390" s="6" t="inlineStr"/>
       <c r="I390" s="6" t="inlineStr"/>
       <c r="J390" s="6" t="inlineStr"/>
+      <c r="K390" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="32" customHeight="1">
       <c r="A391" s="7" t="inlineStr">
@@ -18982,6 +23986,20 @@
       <c r="H391" s="8" t="inlineStr"/>
       <c r="I391" s="8" t="inlineStr"/>
       <c r="J391" s="8" t="inlineStr"/>
+      <c r="K391" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="392" ht="32" customHeight="1">
       <c r="A392" s="5" t="inlineStr">
@@ -19022,6 +24040,20 @@
       <c r="H392" s="6" t="inlineStr"/>
       <c r="I392" s="6" t="inlineStr"/>
       <c r="J392" s="6" t="inlineStr"/>
+      <c r="K392" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="393" ht="32" customHeight="1">
       <c r="A393" s="7" t="inlineStr">
@@ -19102,6 +24134,20 @@
       <c r="H394" s="6" t="inlineStr"/>
       <c r="I394" s="6" t="inlineStr"/>
       <c r="J394" s="6" t="inlineStr"/>
+      <c r="K394" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="395" ht="32" customHeight="1">
       <c r="A395" s="7" t="inlineStr">
@@ -19142,6 +24188,20 @@
       <c r="H395" s="8" t="inlineStr"/>
       <c r="I395" s="8" t="inlineStr"/>
       <c r="J395" s="8" t="inlineStr"/>
+      <c r="K395" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
     </row>
     <row r="396" ht="32" customHeight="1">
       <c r="A396" s="5" t="inlineStr">
@@ -19182,6 +24242,20 @@
       <c r="H396" s="6" t="inlineStr"/>
       <c r="I396" s="6" t="inlineStr"/>
       <c r="J396" s="6" t="inlineStr"/>
+      <c r="K396" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="397" ht="32" customHeight="1">
       <c r="A397" s="7" t="inlineStr">
@@ -19222,6 +24296,20 @@
       <c r="H397" s="8" t="inlineStr"/>
       <c r="I397" s="8" t="inlineStr"/>
       <c r="J397" s="8" t="inlineStr"/>
+      <c r="K397" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="398" ht="32" customHeight="1">
       <c r="A398" s="5" t="inlineStr">
@@ -19262,6 +24350,20 @@
       <c r="H398" s="6" t="inlineStr"/>
       <c r="I398" s="6" t="inlineStr"/>
       <c r="J398" s="6" t="inlineStr"/>
+      <c r="K398" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="399" ht="32" customHeight="1">
       <c r="A399" s="7" t="inlineStr">
@@ -19302,6 +24404,20 @@
       <c r="H399" s="8" t="inlineStr"/>
       <c r="I399" s="8" t="inlineStr"/>
       <c r="J399" s="8" t="inlineStr"/>
+      <c r="K399" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="400" ht="32" customHeight="1">
       <c r="A400" s="5" t="inlineStr">
@@ -19342,6 +24458,20 @@
       <c r="H400" s="6" t="inlineStr"/>
       <c r="I400" s="6" t="inlineStr"/>
       <c r="J400" s="6" t="inlineStr"/>
+      <c r="K400" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>34.6</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="401" ht="32" customHeight="1">
       <c r="A401" s="7" t="inlineStr">
@@ -19702,6 +24832,20 @@
       <c r="H409" s="8" t="inlineStr"/>
       <c r="I409" s="8" t="inlineStr"/>
       <c r="J409" s="8" t="inlineStr"/>
+      <c r="K409" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="32" customHeight="1">
       <c r="A410" s="5" t="inlineStr">
@@ -19822,6 +24966,20 @@
       <c r="H412" s="6" t="inlineStr"/>
       <c r="I412" s="6" t="inlineStr"/>
       <c r="J412" s="6" t="inlineStr"/>
+      <c r="K412" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="413" ht="32" customHeight="1">
       <c r="A413" s="7" t="inlineStr">
@@ -19942,6 +25100,20 @@
       <c r="H415" s="8" t="inlineStr"/>
       <c r="I415" s="8" t="inlineStr"/>
       <c r="J415" s="8" t="inlineStr"/>
+      <c r="K415" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="416" ht="32" customHeight="1">
       <c r="A416" s="5" t="inlineStr">
@@ -20182,6 +25354,20 @@
       <c r="H421" s="8" t="inlineStr"/>
       <c r="I421" s="8" t="inlineStr"/>
       <c r="J421" s="8" t="inlineStr"/>
+      <c r="K421" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="32" customHeight="1">
       <c r="A422" s="5" t="inlineStr">
@@ -20222,6 +25408,20 @@
       <c r="H422" s="6" t="inlineStr"/>
       <c r="I422" s="6" t="inlineStr"/>
       <c r="J422" s="6" t="inlineStr"/>
+      <c r="K422" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="423" ht="32" customHeight="1">
       <c r="A423" s="7" t="inlineStr">
@@ -20302,6 +25502,20 @@
       <c r="H424" s="6" t="inlineStr"/>
       <c r="I424" s="6" t="inlineStr"/>
       <c r="J424" s="6" t="inlineStr"/>
+      <c r="K424" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
     </row>
     <row r="425" ht="32" customHeight="1">
       <c r="A425" s="7" t="inlineStr">
@@ -20342,6 +25556,20 @@
       <c r="H425" s="8" t="inlineStr"/>
       <c r="I425" s="8" t="inlineStr"/>
       <c r="J425" s="8" t="inlineStr"/>
+      <c r="K425" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="426" ht="32" customHeight="1">
       <c r="A426" s="5" t="inlineStr">
@@ -20462,6 +25690,20 @@
       <c r="H428" s="6" t="inlineStr"/>
       <c r="I428" s="6" t="inlineStr"/>
       <c r="J428" s="6" t="inlineStr"/>
+      <c r="K428" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="429" ht="32" customHeight="1">
       <c r="A429" s="7" t="inlineStr">
@@ -20502,6 +25744,20 @@
       <c r="H429" s="8" t="inlineStr"/>
       <c r="I429" s="8" t="inlineStr"/>
       <c r="J429" s="8" t="inlineStr"/>
+      <c r="K429" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr"/>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="430" ht="32" customHeight="1">
       <c r="A430" s="5" t="inlineStr">
@@ -20542,6 +25798,20 @@
       <c r="H430" s="6" t="inlineStr"/>
       <c r="I430" s="6" t="inlineStr"/>
       <c r="J430" s="6" t="inlineStr"/>
+      <c r="K430" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr"/>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="431" ht="32" customHeight="1">
       <c r="A431" s="7" t="inlineStr">
@@ -20622,6 +25892,20 @@
       <c r="H432" s="6" t="inlineStr"/>
       <c r="I432" s="6" t="inlineStr"/>
       <c r="J432" s="6" t="inlineStr"/>
+      <c r="K432" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr"/>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="433" ht="32" customHeight="1">
       <c r="A433" s="7" t="inlineStr">
@@ -20702,6 +25986,20 @@
       <c r="H434" s="6" t="inlineStr"/>
       <c r="I434" s="6" t="inlineStr"/>
       <c r="J434" s="6" t="inlineStr"/>
+      <c r="K434" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="435" ht="32" customHeight="1">
       <c r="A435" s="7" t="inlineStr">
@@ -20742,6 +26040,20 @@
       <c r="H435" s="8" t="inlineStr"/>
       <c r="I435" s="8" t="inlineStr"/>
       <c r="J435" s="8" t="inlineStr"/>
+      <c r="K435" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr"/>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="436" ht="32" customHeight="1">
       <c r="A436" s="5" t="inlineStr">
@@ -20862,6 +26174,20 @@
       <c r="H438" s="6" t="inlineStr"/>
       <c r="I438" s="6" t="inlineStr"/>
       <c r="J438" s="6" t="inlineStr"/>
+      <c r="K438" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="439" ht="32" customHeight="1">
       <c r="A439" s="7" t="inlineStr">
@@ -20902,6 +26228,20 @@
       <c r="H439" s="8" t="inlineStr"/>
       <c r="I439" s="8" t="inlineStr"/>
       <c r="J439" s="8" t="inlineStr"/>
+      <c r="K439" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="32" customHeight="1">
       <c r="A440" s="5" t="inlineStr">
@@ -21102,6 +26442,20 @@
       <c r="H444" s="6" t="inlineStr"/>
       <c r="I444" s="6" t="inlineStr"/>
       <c r="J444" s="6" t="inlineStr"/>
+      <c r="K444" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="445" ht="32" customHeight="1">
       <c r="A445" s="7" t="inlineStr">
@@ -21142,6 +26496,20 @@
       <c r="H445" s="8" t="inlineStr"/>
       <c r="I445" s="8" t="inlineStr"/>
       <c r="J445" s="8" t="inlineStr"/>
+      <c r="K445" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="446" ht="32" customHeight="1">
       <c r="A446" s="5" t="inlineStr">
@@ -21222,6 +26590,20 @@
       <c r="H447" s="8" t="inlineStr"/>
       <c r="I447" s="8" t="inlineStr"/>
       <c r="J447" s="8" t="inlineStr"/>
+      <c r="K447" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr"/>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="448" ht="32" customHeight="1">
       <c r="A448" s="5" t="inlineStr">
@@ -21342,6 +26724,20 @@
       <c r="H450" s="6" t="inlineStr"/>
       <c r="I450" s="6" t="inlineStr"/>
       <c r="J450" s="6" t="inlineStr"/>
+      <c r="K450" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr"/>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="451" ht="32" customHeight="1">
       <c r="A451" s="7" t="inlineStr">
@@ -21462,6 +26858,20 @@
       <c r="H453" s="8" t="inlineStr"/>
       <c r="I453" s="8" t="inlineStr"/>
       <c r="J453" s="8" t="inlineStr"/>
+      <c r="K453" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr"/>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
     </row>
     <row r="454" ht="32" customHeight="1">
       <c r="A454" s="5" t="inlineStr">
@@ -21582,6 +26992,20 @@
       <c r="H456" s="6" t="inlineStr"/>
       <c r="I456" s="6" t="inlineStr"/>
       <c r="J456" s="6" t="inlineStr"/>
+      <c r="K456" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr"/>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="457" ht="32" customHeight="1">
       <c r="A457" s="7" t="inlineStr">
@@ -21622,6 +27046,20 @@
       <c r="H457" s="8" t="inlineStr"/>
       <c r="I457" s="8" t="inlineStr"/>
       <c r="J457" s="8" t="inlineStr"/>
+      <c r="K457" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr"/>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="458" ht="32" customHeight="1">
       <c r="A458" s="5" t="inlineStr">
@@ -21782,6 +27220,20 @@
       <c r="H461" s="8" t="inlineStr"/>
       <c r="I461" s="8" t="inlineStr"/>
       <c r="J461" s="8" t="inlineStr"/>
+      <c r="K461" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr"/>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="462" ht="48" customHeight="1">
       <c r="A462" s="5" t="inlineStr">
@@ -21824,6 +27276,20 @@
       <c r="J462" s="6" t="inlineStr">
         <is>
           <t>2000</t>
+        </is>
+      </c>
+      <c r="K462" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>21.3</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr"/>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>9.5</t>
         </is>
       </c>
     </row>
